--- a/Viajante/BD/VEÍCULOS.xlsx
+++ b/Viajante/BD/VEÍCULOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perna\Desktop\STALLANTIS\BC TURBO\BC Turbo App\Viajante\BD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{757B48C5-5FA0-49E2-887E-4D688D2989ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00F2135A-63FB-4A46-825F-9EDDEE265199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B427D6DB-B8A3-4F9A-8655-534208414879}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B427D6DB-B8A3-4F9A-8655-534208414879}"/>
   </bookViews>
   <sheets>
     <sheet name="VEÍCULOS" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="42">
   <si>
     <t>COD VEICULO</t>
   </si>
@@ -159,6 +159,9 @@
   </si>
   <si>
     <t>VEÍCULO 3/4</t>
+  </si>
+  <si>
+    <t>TRUCK SIDER</t>
   </si>
 </sst>
 </file>
@@ -552,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5290EA8C-EB11-4CF4-B41B-163A359A632F}">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.26953125" bestFit="1" customWidth="1"/>
@@ -649,84 +652,84 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="7">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="D6" s="5">
-        <v>61.199999999999996</v>
+        <v>57.11999999999999</v>
       </c>
       <c r="E6" s="6">
         <v>12000</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="9">
-        <v>4</v>
+      <c r="A7" s="7">
+        <v>13</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D7" s="5">
-        <v>94.080000000000013</v>
+        <v>61.199999999999996</v>
       </c>
       <c r="E7" s="6">
-        <v>25000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" s="5">
         <v>94.080000000000013</v>
       </c>
       <c r="E8" s="6">
-        <v>34000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="9">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D9" s="5">
-        <v>106.07999999999998</v>
+        <v>94.080000000000013</v>
       </c>
       <c r="E9" s="6">
-        <v>25000</v>
+        <v>34000</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="9">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D10" s="5">
-        <v>108</v>
+        <v>106.07999999999998</v>
       </c>
       <c r="E10" s="6">
         <v>25000</v>
@@ -734,152 +737,152 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="D11" s="5">
-        <v>161.27999999999997</v>
+        <v>108</v>
       </c>
       <c r="E11" s="6">
-        <v>45500</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
+        <v>7</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="5">
+        <v>161.27999999999997</v>
+      </c>
+      <c r="E12" s="6">
+        <v>45500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="9">
         <v>8</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B13" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C13" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D13" s="5">
         <v>162</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E13" s="6">
         <v>48000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="6">
-        <v>11</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="5">
-        <v>2.04</v>
-      </c>
-      <c r="E13" s="6">
-        <v>500</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="6">
+        <v>11</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="5">
+        <v>2.04</v>
+      </c>
+      <c r="E14" s="6">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="6">
         <v>10</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B15" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C15" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D15" s="5">
         <v>6.2720000000000002</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E15" s="6">
         <v>1200</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="9">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="9">
         <v>14</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B16" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C16" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D16" s="5">
         <v>94.080000000000013</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E16" s="6">
         <v>25000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="7">
-        <v>15</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="5">
-        <v>33.234935999999998</v>
-      </c>
-      <c r="E16" s="6">
-        <v>21920</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D17" s="5">
-        <v>75.275076999999996</v>
+        <v>33.234935999999998</v>
       </c>
       <c r="E17" s="6">
-        <v>26512</v>
+        <v>21920</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D18" s="5">
-        <v>75.263999999999996</v>
+        <v>75.275076999999996</v>
       </c>
       <c r="E18" s="6">
-        <v>13000</v>
+        <v>26512</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D19" s="5">
-        <v>80.64</v>
+        <v>75.263999999999996</v>
       </c>
       <c r="E19" s="6">
         <v>13000</v>
@@ -887,23 +890,40 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="7">
+        <v>18</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="5">
+        <v>80.64</v>
+      </c>
+      <c r="E20" s="6">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" s="7">
         <v>19</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B21" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C21" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D21" s="5">
         <v>94.080000000000013</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E21" s="6">
         <v>25000</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="K24" s="10"/>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="K25" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Viajante/BD/VEÍCULOS.xlsx
+++ b/Viajante/BD/VEÍCULOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perna\Desktop\STALLANTIS\BC TURBO\BC Turbo App\Viajante\BD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00F2135A-63FB-4A46-825F-9EDDEE265199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E9D499-9B96-49DD-B8C2-2859F5E73307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B427D6DB-B8A3-4F9A-8655-534208414879}"/>
   </bookViews>
